--- a/training_forms/033_hair_product_brand_training_registration_form--training_forms.xlsx
+++ b/training_forms/033_hair_product_brand_training_registration_form--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'haircare',_'value':_'haircare'}</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Haircare', 'value': 'haircare'}</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'skincare',_'value':_'skincare'}</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Skincare', 'value': 'skincare'}</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'fragrance',_'value':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'Fragrance', 'value': 'fragrance'}</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1004,_'label':_'black',_'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1004, 'label': 'Black', 'value': 'black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1005,_'label':_'brown',_'value':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1005, 'label': 'Brown', 'value': 'brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1006,_'label':_'blonde',_'value':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1006, 'label': 'Blonde', 'value': 'blonde'}</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1007,_'label':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1007, 'label': 'Small', 'value': 'small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1008,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1008, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1009,_'label':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1009, 'label': 'Large', 'value': 'large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1010,_'label':_'less_than_1_oz',_'value':_'less_than_1_oz'}</t>
+          <t>less_than_1_oz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1010, 'label': 'Less than 1 oz', 'value': 'less_than_1_oz'}</t>
+          <t>Less than 1 oz</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1011,_'label':_'1-10_oz',_'value':_'1-10_oz'}</t>
+          <t>1-10_oz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1011, 'label': '1-10 oz', 'value': '1-10_oz'}</t>
+          <t>1-10 oz</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1012,_'label':_'11-50_oz',_'value':_'11-50_oz'}</t>
+          <t>11-50_oz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1012, 'label': '11-50 oz', 'value': '11-50_oz'}</t>
+          <t>11-50 oz</t>
         </is>
       </c>
     </row>
